--- a/data/trans_orig/IP2904-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33204</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>47348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63632</t>
+          <t>63382</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84660</t>
+          <t>85794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107001</t>
+          <t>107373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14754</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>31029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>49298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>37938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>37631</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50876</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71184</t>
+          <t>70767</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102504</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128765</t>
+          <t>129506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89565</t>
+          <t>91694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115682</t>
+          <t>115181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200290</t>
+          <t>203453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235219</t>
+          <t>237203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48390</t>
+          <t>48728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69901</t>
+          <t>70056</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>58014</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78782</t>
+          <t>81033</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113496</t>
+          <t>111188</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>144374</t>
+          <t>143495</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62440</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86328</t>
+          <t>86272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67168</t>
+          <t>66215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91121</t>
+          <t>90602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135742</t>
+          <t>136157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169358</t>
+          <t>167262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>51365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>68898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61825</t>
+          <t>61227</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81050</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117738</t>
+          <t>117041</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>143435</t>
+          <t>142938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16666</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30206</t>
+          <t>30178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49864</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72268</t>
+          <t>71087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49194</t>
+          <t>48757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>37060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57462</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80747</t>
+          <t>80489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70778</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92617</t>
+          <t>92251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68732</t>
+          <t>68038</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90020</t>
+          <t>90761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>144632</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175995</t>
+          <t>176424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,19%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35890</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54935</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>48043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89250</t>
+          <t>88001</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>117063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52073</t>
+          <t>51664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>71839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55279</t>
+          <t>54862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75536</t>
+          <t>76579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113748</t>
+          <t>112940</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140715</t>
+          <t>141782</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,32%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276696</t>
+          <t>278296</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317608</t>
+          <t>317733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>288736</t>
+          <t>289489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329705</t>
+          <t>331745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578445</t>
+          <t>578726</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>634669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>130223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>164220</t>
+          <t>164861</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>166375</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205536</t>
+          <t>203473</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>306843</t>
+          <t>306527</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>354995</t>
+          <t>353938</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>187317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225634</t>
+          <t>225327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182447</t>
+          <t>183005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220578</t>
+          <t>220601</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>381633</t>
+          <t>382393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433063</t>
+          <t>433687</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51355</t>
+          <t>50958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69716</t>
+          <t>69596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69587</t>
+          <t>69638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107905</t>
+          <t>105399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132504</t>
+          <t>132402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,66%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>34469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28852</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52289</t>
+          <t>52044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73735</t>
+          <t>75514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31158</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48506</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57736</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79648</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103714</t>
+          <t>103975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>128087</t>
+          <t>128506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117109</t>
+          <t>116436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145898</t>
+          <t>143260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225549</t>
+          <t>229413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>263029</t>
+          <t>264647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>49380</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71164</t>
+          <t>71301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55463</t>
+          <t>56259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79934</t>
+          <t>79479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113156</t>
+          <t>114644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>144659</t>
+          <t>146745</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70440</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55231</t>
+          <t>54907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79563</t>
+          <t>78683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110365</t>
+          <t>110260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142443</t>
+          <t>142902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65889</t>
+          <t>66168</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87683</t>
+          <t>87590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71816</t>
+          <t>70467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>90820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143450</t>
+          <t>142849</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173559</t>
+          <t>172566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>40322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>31457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49830</t>
+          <t>49195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84567</t>
+          <t>82986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58875</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26252</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72357</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97864</t>
+          <t>98894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64384</t>
+          <t>64318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86061</t>
+          <t>85915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72907</t>
+          <t>74158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>94176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143334</t>
+          <t>143523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175219</t>
+          <t>173225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61163</t>
+          <t>60647</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57427</t>
+          <t>57622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>84998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113015</t>
+          <t>113037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32592</t>
+          <t>32449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51096</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54708</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72765</t>
+          <t>73571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>99925</t>
+          <t>100108</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>303964</t>
+          <t>307035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>349135</t>
+          <t>350857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332471</t>
+          <t>333598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>377113</t>
+          <t>378764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>650897</t>
+          <t>654035</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>714500</t>
+          <t>716641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>188361</t>
+          <t>187067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>172078</t>
+          <t>171519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>211044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332316</t>
+          <t>332666</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386578</t>
+          <t>386409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>170323</t>
+          <t>168054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210176</t>
+          <t>207643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157398</t>
+          <t>155120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195737</t>
+          <t>195794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>336186</t>
+          <t>335471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390196</t>
+          <t>388809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,64%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32770</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48964</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42871</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60485</t>
+          <t>59814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80198</t>
+          <t>80467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103912</t>
+          <t>103203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24715</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23734</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>39035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52268</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74753</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63159</t>
+          <t>63212</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85878</t>
+          <t>85882</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78110</t>
+          <t>77545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>99101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88183</t>
+          <t>86824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113998</t>
+          <t>112783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170899</t>
+          <t>172327</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>205107</t>
+          <t>206820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,62%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>47060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66678</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61620</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>84374</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>113009</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143505</t>
+          <t>144766</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>54402</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73174</t>
+          <t>74553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70529</t>
+          <t>71173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94444</t>
+          <t>94457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129353</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161912</t>
+          <t>164427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>72954</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95129</t>
+          <t>94116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>63511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>86250</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>141618</t>
+          <t>144321</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>175349</t>
+          <t>174411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46212</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>67370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>51440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83535</t>
+          <t>84946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>114185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36534</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56173</t>
+          <t>56452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>57163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78243</t>
+          <t>77757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,47 +6944,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>31,01%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>114088</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>98727</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>129098</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>42,44%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>114088</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>99018</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>129748</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73132</t>
+          <t>73218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94702</t>
+          <t>93766</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>63373</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>84433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>142328</t>
+          <t>141341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171281</t>
+          <t>172205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>27435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67765</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93319</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36799</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>34471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52861</t>
+          <t>52799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77449</t>
+          <t>77617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104735</t>
+          <t>104151</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277523</t>
+          <t>275526</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318552</t>
+          <t>315396</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>279414</t>
+          <t>277987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>320163</t>
+          <t>324235</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>569025</t>
+          <t>565086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>626839</t>
+          <t>628218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>161078</t>
+          <t>160146</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>197553</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>170184</t>
+          <t>170292</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>208488</t>
+          <t>208137</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>342735</t>
+          <t>340659</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>396319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182029</t>
+          <t>183560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>222075</t>
+          <t>221708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202377</t>
+          <t>200266</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>241971</t>
+          <t>242740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>396580</t>
+          <t>394293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>452493</t>
+          <t>453292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2904-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2904-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>55437</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47174</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63588</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,08%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40444</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32913</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48082</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33422</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48370</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>44,34%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>55437</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>47348</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>63382</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85794</t>
+          <t>84620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107373</t>
+          <t>107637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,02%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19197</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13431</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26074</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20526</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14340</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27157</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14431</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27231</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>22,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19197</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13450</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25863</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31029</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49298</t>
+          <t>48945</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>29800</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22938</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37901</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>30238</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23728</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37938</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23913</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>37914</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>33,15%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29800</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22933</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>37631</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>28,53%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>50550</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70767</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104433</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>104433</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>104433</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91208</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91208</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91208</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>104433</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>104433</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>104433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103667</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91371</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>116446</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>36,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115648</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103885</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>129506</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>103835</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>128481</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>46,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>103667</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>91694</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>115181</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>41,43%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203453</t>
+          <t>202205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>237203</t>
+          <t>236884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68586</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58063</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>79975</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>27,41%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>31,96%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>58663</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>48728</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>70056</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>48604</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>69908</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>23,64%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>68586</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>58014</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>81033</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111188</t>
+          <t>112373</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143495</t>
+          <t>143537</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77988</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66788</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>89906</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>73813</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>62108</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>86272</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61792</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>85568</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,75%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>77988</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66215</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90602</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136157</t>
+          <t>136920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167262</t>
+          <t>169295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>250241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>372</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>248124</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>248124</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>248124</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>250241</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70689</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>61237</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80229</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>51,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>44,57%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>58,4%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>59851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51365</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68898</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>50919</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>68790</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>48,83%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>41,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70689</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>61227</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>80010</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>51,45%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117041</t>
+          <t>118056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142938</t>
+          <t>144909</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37984</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29888</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46723</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>22667</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16103</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29884</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16608</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30611</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37984</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30178</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>47727</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>50244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71087</t>
+          <t>72513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28708</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21295</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36236</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>40046</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>31796</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48757</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32199</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49067</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28708</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21384</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>37060</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56548</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80489</t>
+          <t>80795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>137381</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>137381</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>137381</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122563</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122563</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122563</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>137381</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>137381</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>137381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,67 +2095,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>79004</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>68749</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>90196</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>81554</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>70203</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92251</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71627</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>92192</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>43,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>79004</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>68038</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>90761</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>145166</t>
+          <t>145539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>176876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>57987</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>48394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>68081</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>23,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>45105</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>35704</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>55118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>36717</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>54201</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>57987</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>48043</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>69715</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88001</t>
+          <t>89919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117063</t>
+          <t>117571</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>64936</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>55022</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>74889</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>27,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>37,09%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>61781</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>51664</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>71839</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>52030</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>71930</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>32,79%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>64936</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>54862</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>76579</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>32,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>112940</t>
+          <t>111437</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141782</t>
+          <t>140319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>201927</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>201927</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>201927</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>188441</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>201927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>308797</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>288011</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>328546</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>41,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>447</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>297498</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>278296</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>317733</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>275889</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>319201</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>45,75%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,79%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>48,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>308797</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>289489</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>331745</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>578726</t>
+          <t>577925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>634669</t>
+          <t>633820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>183754</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>165560</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>202309</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,86%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>146960</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>130223</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>164861</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>130030</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>163916</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>22,6%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>25,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>183754</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>164503</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>203473</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>306527</t>
+          <t>308439</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>353938</t>
+          <t>357243</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>201431</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>182824</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>221273</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>205878</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>187317</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>225327</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>184787</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>222901</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>31,66%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>201431</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>183005</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>220601</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382393</t>
+          <t>380426</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433687</t>
+          <t>434364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>693982</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>650336</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>693982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59415</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50020</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68786</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>60465</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>50958</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69596</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51167</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69229</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59415</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50056</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>69638</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>47,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105399</t>
+          <t>106160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132402</t>
+          <t>132104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,54%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36484</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28738</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>45705</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26281</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19492</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34469</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19510</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34491</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>20,91%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36484</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28177</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>45513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75514</t>
+          <t>74394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29859</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22689</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38060</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18,04%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>30,26%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>38909</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31177</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48290</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>30824</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47807</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>30,96%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29859</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22145</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38770</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56715</t>
+          <t>58462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>81773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125758</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125758</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125758</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>125655</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>125655</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>125655</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>125758</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>125758</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>125758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>130215</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>117114</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>143428</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>49,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115475</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103975</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>128506</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102991</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>129262</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>49,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>130215</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>116436</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>143260</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229413</t>
+          <t>225165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>264647</t>
+          <t>264567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68086</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56501</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80541</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25,7%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>30,4%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>59860</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>49380</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>71301</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>49268</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>72317</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>25,55%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>30,43%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>68086</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>56259</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>79479</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114644</t>
+          <t>112479</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146745</t>
+          <t>144711</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66611</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55837</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79343</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>58947</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48934</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69967</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>48485</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66611</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>54907</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78683</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110260</t>
+          <t>110812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142902</t>
+          <t>142234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>264912</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>234283</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>234283</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>234283</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>264912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>81444</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70153</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>91190</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>52,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>45,02%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>77257</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>66168</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>87590</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>67706</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>88272</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>49,19%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>42,13%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>81444</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70467</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>90820</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>52,26%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142849</t>
+          <t>144853</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172566</t>
+          <t>174047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39716</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31435</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49382</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30800</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23022</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40322</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23380</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39864</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>39716</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31457</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49195</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>59518</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82986</t>
+          <t>82468</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34675</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27104</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43956</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>48986</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39486</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59093</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40417</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>58544</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>31,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>34675</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26423</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>43800</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>70553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98894</t>
+          <t>96585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>155835</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>155835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>83783</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73198</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95078</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>75117</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>64318</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85915</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>64426</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85008</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,98%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>38,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>83783</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>74158</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>94176</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143523</t>
+          <t>145554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173225</t>
+          <t>173591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -4720,67 +4720,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>47475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>38574</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>58336</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>50828</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41113</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>60647</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>42490</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>60879</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>47475</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>38022</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>57622</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84998</t>
+          <t>83842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113037</t>
+          <t>110735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44697</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>55023</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>25,4%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41068</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32449</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50506</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>32812</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>50280</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>24,59%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44697</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>36643</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54409</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>25,4%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73571</t>
+          <t>73695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100108</t>
+          <t>99568</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>175955</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>175955</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>175955</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>167013</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>175955</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>175955</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>175955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>354857</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>332377</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>375027</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>49,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>46,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>51,91%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>328315</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>307035</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>350857</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>307161</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>348445</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>48,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>51,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>354857</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>333598</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>378764</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>49,12%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>654035</t>
+          <t>653849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>716641</t>
+          <t>719828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>191760</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>173106</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>210210</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,1%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>167770</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>149475</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>187067</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>149188</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>186155</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>24,53%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>21,85%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>27,35%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>191760</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>171519</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>211044</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332666</t>
+          <t>333220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>386409</t>
+          <t>385400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>175843</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>157093</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>195180</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>24,34%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>21,74%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>187911</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>168054</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>207643</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>168498</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>207282</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>27,47%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,57%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>175843</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>155120</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>195794</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335471</t>
+          <t>336730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>388809</t>
+          <t>388580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>722460</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>985</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>683995</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>722460</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51236</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42376</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>59640</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40360</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32280</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48538</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32655</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48995</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>34,68%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>51236</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>42345</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>59814</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80467</t>
+          <t>80092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>102623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30705</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23987</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>38229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,19%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31539</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23335</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39283</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24214</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39250</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,1%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30705</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23317</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39035</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>73092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29888</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22650</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38386</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20,25%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>44472</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36146</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53222</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36424</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>53625</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>38,22%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29888</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22017</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>36947</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63212</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>111828</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>111828</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>111828</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>116370</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>116370</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>116370</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>111828</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>111828</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>111828</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100439</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88179</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112880</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>44,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>88982</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77545</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99101</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77781</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100864</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>42,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>47,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100439</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86824</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112783</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172327</t>
+          <t>172504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>206820</t>
+          <t>208675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>72356</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>60593</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83454</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>56023</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>47060</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>46840</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>66373</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>26,85%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,55%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>72356</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>61215</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>84374</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113009</t>
+          <t>114278</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>144766</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82088</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>71233</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95413</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>63673</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54402</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>74553</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>75060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>30,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,73%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82088</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>71173</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>94457</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131338</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164427</t>
+          <t>161505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>254884</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>254884</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>254884</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>208678</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>254884</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>254884</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>254884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75066</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>64902</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86759</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>40,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>47,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>83394</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>72954</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>72308</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>94316</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,18%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75066</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>63511</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86250</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>40,72%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144321</t>
+          <t>142320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174411</t>
+          <t>174858</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41878</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32996</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52088</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>56126</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46313</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>67370</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>46386</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>67385</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>41878</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32995</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>51440</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84946</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114185</t>
+          <t>113047</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67411</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>56897</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>77331</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>30,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46677</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>37384</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56452</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37277</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>57628</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>25,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>67411</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57163</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77757</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98727</t>
+          <t>97947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129098</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184356</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186197</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186197</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186197</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73646</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62775</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84635</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>38,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>83608</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>73218</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>93766</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>72866</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>95366</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>73646</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>63373</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>84433</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141341</t>
+          <t>141037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172205</t>
+          <t>172552</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44322</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>34812</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>55176</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>27,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>27435</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>45113</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>26967</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>44964</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44322</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>34706</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>54195</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>27,48%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>66783</t>
+          <t>66937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>93089</t>
+          <t>94280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>43300</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>34183</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>53540</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>26,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>21,2%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33,2%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>46785</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>37347</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56770</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>37105</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>56914</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>28,27%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>34,3%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43300</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>34471</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>52799</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77617</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>104151</t>
+          <t>104518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>161267</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>161267</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>161267</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>165515</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>165515</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>165515</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>161267</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>161267</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>161267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>300387</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>280570</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>323746</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>42,17%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>39,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>45,45%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>296343</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>275526</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>315396</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>276218</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>319409</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>43,79%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>300387</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>277987</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>324235</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>42,17%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>565086</t>
+          <t>565277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628218</t>
+          <t>624509</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>189261</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>168915</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>208042</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>29,21%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>178810</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>160146</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>197553</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>160581</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197992</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>26,42%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>189261</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>170292</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>208137</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>340659</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>396319</t>
+          <t>396503</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>222687</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>202016</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>243441</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>31,26%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>304</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>201607</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>183560</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>221708</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>184040</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>222837</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>29,79%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>27,12%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>222687</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>200266</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>242740</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>394293</t>
+          <t>397030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>453292</t>
+          <t>453558</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712335</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>676760</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
